--- a/samples/ss_cbatu12_dltms_ingest.xlsx
+++ b/samples/ss_cbatu12_dltms_ingest.xlsx
@@ -632,31 +632,21 @@
           <t>500 kV</t>
         </is>
       </c>
-      <c r="G2" t="inlineStr"/>
-      <c r="H2" t="inlineStr"/>
-      <c r="I2" t="inlineStr"/>
-      <c r="J2" t="inlineStr"/>
-      <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
-      <c r="M2" t="inlineStr"/>
       <c r="N2" t="inlineStr">
         <is>
           <t>Beroperasi</t>
         </is>
       </c>
-      <c r="O2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
           <t>Normal</t>
         </is>
       </c>
-      <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
         <is>
           <t>Jawa Barat</t>
         </is>
       </c>
-      <c r="S2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -703,15 +693,11 @@
       <c r="J3" t="n">
         <v>1</v>
       </c>
-      <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr"/>
       <c r="N3" t="inlineStr">
         <is>
           <t>Beroperasi</t>
         </is>
       </c>
-      <c r="O3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
           <t>Rawan</t>
@@ -727,7 +713,6 @@
           <t>Jawa Barat</t>
         </is>
       </c>
-      <c r="S3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -774,15 +759,11 @@
       <c r="J4" t="n">
         <v>1</v>
       </c>
-      <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr"/>
       <c r="N4" t="inlineStr">
         <is>
           <t>Beroperasi</t>
         </is>
       </c>
-      <c r="O4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
           <t>Rawan</t>
@@ -798,7 +779,6 @@
           <t>Jawa Barat</t>
         </is>
       </c>
-      <c r="S4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -827,31 +807,21 @@
           <t>500 kV</t>
         </is>
       </c>
-      <c r="G5" t="inlineStr"/>
-      <c r="H5" t="inlineStr"/>
-      <c r="I5" t="inlineStr"/>
-      <c r="J5" t="inlineStr"/>
-      <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr"/>
-      <c r="M5" t="inlineStr"/>
       <c r="N5" t="inlineStr">
         <is>
           <t>Beroperasi</t>
         </is>
       </c>
-      <c r="O5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
           <t>Normal</t>
         </is>
       </c>
-      <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
         <is>
           <t>Jawa Barat</t>
         </is>
       </c>
-      <c r="S5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -898,15 +868,11 @@
       <c r="J6" t="n">
         <v>1</v>
       </c>
-      <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr"/>
-      <c r="M6" t="inlineStr"/>
       <c r="N6" t="inlineStr">
         <is>
           <t>Beroperasi</t>
         </is>
       </c>
-      <c r="O6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
           <t>Rawan</t>
@@ -922,7 +888,6 @@
           <t>Jawa Barat</t>
         </is>
       </c>
-      <c r="S6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -969,15 +934,11 @@
       <c r="J7" t="n">
         <v>1</v>
       </c>
-      <c r="K7" t="inlineStr"/>
-      <c r="L7" t="inlineStr"/>
-      <c r="M7" t="inlineStr"/>
       <c r="N7" t="inlineStr">
         <is>
           <t>Beroperasi</t>
         </is>
       </c>
-      <c r="O7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
           <t>Rawan</t>
@@ -993,7 +954,6 @@
           <t>Jawa Barat</t>
         </is>
       </c>
-      <c r="S7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1040,15 +1000,11 @@
       <c r="J8" t="n">
         <v>1</v>
       </c>
-      <c r="K8" t="inlineStr"/>
-      <c r="L8" t="inlineStr"/>
-      <c r="M8" t="inlineStr"/>
       <c r="N8" t="inlineStr">
         <is>
           <t>Beroperasi</t>
         </is>
       </c>
-      <c r="O8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
           <t>Rawan</t>
@@ -1064,7 +1020,6 @@
           <t>Jawa Barat</t>
         </is>
       </c>
-      <c r="S8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1111,15 +1066,11 @@
       <c r="J9" t="n">
         <v>1</v>
       </c>
-      <c r="K9" t="inlineStr"/>
-      <c r="L9" t="inlineStr"/>
-      <c r="M9" t="inlineStr"/>
       <c r="N9" t="inlineStr">
         <is>
           <t>Beroperasi</t>
         </is>
       </c>
-      <c r="O9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
           <t>Rawan</t>
@@ -1135,7 +1086,6 @@
           <t>Jawa Barat</t>
         </is>
       </c>
-      <c r="S9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1164,31 +1114,21 @@
           <t>150 kV</t>
         </is>
       </c>
-      <c r="G10" t="inlineStr"/>
-      <c r="H10" t="inlineStr"/>
-      <c r="I10" t="inlineStr"/>
-      <c r="J10" t="inlineStr"/>
-      <c r="K10" t="inlineStr"/>
-      <c r="L10" t="inlineStr"/>
-      <c r="M10" t="inlineStr"/>
       <c r="N10" t="inlineStr">
         <is>
           <t>Beroperasi</t>
         </is>
       </c>
-      <c r="O10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
           <t>Normal</t>
         </is>
       </c>
-      <c r="Q10" t="inlineStr"/>
       <c r="R10" t="inlineStr">
         <is>
           <t>Jawa Barat</t>
         </is>
       </c>
-      <c r="S10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1217,35 +1157,26 @@
           <t>150 kV</t>
         </is>
       </c>
-      <c r="G11" t="inlineStr"/>
-      <c r="H11" t="inlineStr"/>
-      <c r="I11" t="inlineStr"/>
-      <c r="J11" t="inlineStr"/>
-      <c r="K11" t="inlineStr"/>
       <c r="L11" t="inlineStr">
         <is>
           <t>bus section + kopel</t>
         </is>
       </c>
-      <c r="M11" t="inlineStr"/>
       <c r="N11" t="inlineStr">
         <is>
           <t>Beroperasi</t>
         </is>
       </c>
-      <c r="O11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
           <t>Normal</t>
         </is>
       </c>
-      <c r="Q11" t="inlineStr"/>
       <c r="R11" t="inlineStr">
         <is>
           <t>Jawa Barat</t>
         </is>
       </c>
-      <c r="S11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1274,31 +1205,21 @@
           <t>150 kV</t>
         </is>
       </c>
-      <c r="G12" t="inlineStr"/>
-      <c r="H12" t="inlineStr"/>
-      <c r="I12" t="inlineStr"/>
-      <c r="J12" t="inlineStr"/>
-      <c r="K12" t="inlineStr"/>
-      <c r="L12" t="inlineStr"/>
-      <c r="M12" t="inlineStr"/>
       <c r="N12" t="inlineStr">
         <is>
           <t>Beroperasi</t>
         </is>
       </c>
-      <c r="O12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
           <t>Normal</t>
         </is>
       </c>
-      <c r="Q12" t="inlineStr"/>
       <c r="R12" t="inlineStr">
         <is>
           <t>Jawa Barat</t>
         </is>
       </c>
-      <c r="S12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1327,19 +1248,11 @@
           <t>150 kV</t>
         </is>
       </c>
-      <c r="G13" t="inlineStr"/>
-      <c r="H13" t="inlineStr"/>
-      <c r="I13" t="inlineStr"/>
-      <c r="J13" t="inlineStr"/>
-      <c r="K13" t="inlineStr"/>
-      <c r="L13" t="inlineStr"/>
-      <c r="M13" t="inlineStr"/>
       <c r="N13" t="inlineStr">
         <is>
           <t>Beroperasi</t>
         </is>
       </c>
-      <c r="O13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
           <t>Rawan</t>
@@ -1355,7 +1268,6 @@
           <t>Jawa Barat</t>
         </is>
       </c>
-      <c r="S13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -1384,31 +1296,21 @@
           <t>150 kV</t>
         </is>
       </c>
-      <c r="G14" t="inlineStr"/>
-      <c r="H14" t="inlineStr"/>
-      <c r="I14" t="inlineStr"/>
-      <c r="J14" t="inlineStr"/>
-      <c r="K14" t="inlineStr"/>
-      <c r="L14" t="inlineStr"/>
-      <c r="M14" t="inlineStr"/>
       <c r="N14" t="inlineStr">
         <is>
           <t>Beroperasi</t>
         </is>
       </c>
-      <c r="O14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
           <t>Normal</t>
         </is>
       </c>
-      <c r="Q14" t="inlineStr"/>
       <c r="R14" t="inlineStr">
         <is>
           <t>Jawa Barat</t>
         </is>
       </c>
-      <c r="S14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -1437,31 +1339,21 @@
           <t>150 kV</t>
         </is>
       </c>
-      <c r="G15" t="inlineStr"/>
-      <c r="H15" t="inlineStr"/>
-      <c r="I15" t="inlineStr"/>
-      <c r="J15" t="inlineStr"/>
-      <c r="K15" t="inlineStr"/>
-      <c r="L15" t="inlineStr"/>
-      <c r="M15" t="inlineStr"/>
       <c r="N15" t="inlineStr">
         <is>
           <t>Beroperasi</t>
         </is>
       </c>
-      <c r="O15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
           <t>Normal</t>
         </is>
       </c>
-      <c r="Q15" t="inlineStr"/>
       <c r="R15" t="inlineStr">
         <is>
           <t>Jawa Barat</t>
         </is>
       </c>
-      <c r="S15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -1490,31 +1382,21 @@
           <t>150 kV</t>
         </is>
       </c>
-      <c r="G16" t="inlineStr"/>
-      <c r="H16" t="inlineStr"/>
-      <c r="I16" t="inlineStr"/>
-      <c r="J16" t="inlineStr"/>
-      <c r="K16" t="inlineStr"/>
-      <c r="L16" t="inlineStr"/>
-      <c r="M16" t="inlineStr"/>
       <c r="N16" t="inlineStr">
         <is>
           <t>Beroperasi</t>
         </is>
       </c>
-      <c r="O16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
           <t>Normal</t>
         </is>
       </c>
-      <c r="Q16" t="inlineStr"/>
       <c r="R16" t="inlineStr">
         <is>
           <t>Jawa Barat</t>
         </is>
       </c>
-      <c r="S16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -1543,31 +1425,21 @@
           <t>150 kV</t>
         </is>
       </c>
-      <c r="G17" t="inlineStr"/>
-      <c r="H17" t="inlineStr"/>
-      <c r="I17" t="inlineStr"/>
-      <c r="J17" t="inlineStr"/>
-      <c r="K17" t="inlineStr"/>
-      <c r="L17" t="inlineStr"/>
-      <c r="M17" t="inlineStr"/>
       <c r="N17" t="inlineStr">
         <is>
           <t>Beroperasi</t>
         </is>
       </c>
-      <c r="O17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
           <t>Normal</t>
         </is>
       </c>
-      <c r="Q17" t="inlineStr"/>
       <c r="R17" t="inlineStr">
         <is>
           <t>Jawa Barat</t>
         </is>
       </c>
-      <c r="S17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -1596,19 +1468,11 @@
           <t>150 kV</t>
         </is>
       </c>
-      <c r="G18" t="inlineStr"/>
-      <c r="H18" t="inlineStr"/>
-      <c r="I18" t="inlineStr"/>
-      <c r="J18" t="inlineStr"/>
-      <c r="K18" t="inlineStr"/>
-      <c r="L18" t="inlineStr"/>
-      <c r="M18" t="inlineStr"/>
       <c r="N18" t="inlineStr">
         <is>
           <t>Beroperasi</t>
         </is>
       </c>
-      <c r="O18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
           <t>Rawan</t>
@@ -1624,7 +1488,6 @@
           <t>Jawa Barat</t>
         </is>
       </c>
-      <c r="S18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -1653,31 +1516,21 @@
           <t>150 kV</t>
         </is>
       </c>
-      <c r="G19" t="inlineStr"/>
-      <c r="H19" t="inlineStr"/>
-      <c r="I19" t="inlineStr"/>
-      <c r="J19" t="inlineStr"/>
-      <c r="K19" t="inlineStr"/>
-      <c r="L19" t="inlineStr"/>
-      <c r="M19" t="inlineStr"/>
       <c r="N19" t="inlineStr">
         <is>
           <t>Beroperasi</t>
         </is>
       </c>
-      <c r="O19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
           <t>Normal</t>
         </is>
       </c>
-      <c r="Q19" t="inlineStr"/>
       <c r="R19" t="inlineStr">
         <is>
           <t>Jawa Barat</t>
         </is>
       </c>
-      <c r="S19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -1706,31 +1559,21 @@
           <t>150 kV</t>
         </is>
       </c>
-      <c r="G20" t="inlineStr"/>
-      <c r="H20" t="inlineStr"/>
-      <c r="I20" t="inlineStr"/>
-      <c r="J20" t="inlineStr"/>
-      <c r="K20" t="inlineStr"/>
-      <c r="L20" t="inlineStr"/>
-      <c r="M20" t="inlineStr"/>
       <c r="N20" t="inlineStr">
         <is>
           <t>Beroperasi</t>
         </is>
       </c>
-      <c r="O20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
           <t>Normal</t>
         </is>
       </c>
-      <c r="Q20" t="inlineStr"/>
       <c r="R20" t="inlineStr">
         <is>
           <t>Jawa Barat</t>
         </is>
       </c>
-      <c r="S20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -1759,19 +1602,11 @@
           <t>150 kV</t>
         </is>
       </c>
-      <c r="G21" t="inlineStr"/>
-      <c r="H21" t="inlineStr"/>
-      <c r="I21" t="inlineStr"/>
-      <c r="J21" t="inlineStr"/>
-      <c r="K21" t="inlineStr"/>
-      <c r="L21" t="inlineStr"/>
-      <c r="M21" t="inlineStr"/>
       <c r="N21" t="inlineStr">
         <is>
           <t>Beroperasi</t>
         </is>
       </c>
-      <c r="O21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
           <t>Rawan</t>
@@ -1787,7 +1622,6 @@
           <t>Jawa Barat</t>
         </is>
       </c>
-      <c r="S21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -1816,35 +1650,26 @@
           <t>150 kV</t>
         </is>
       </c>
-      <c r="G22" t="inlineStr"/>
-      <c r="H22" t="inlineStr"/>
-      <c r="I22" t="inlineStr"/>
-      <c r="J22" t="inlineStr"/>
-      <c r="K22" t="inlineStr"/>
       <c r="L22" t="inlineStr">
         <is>
           <t>bus section + kopel</t>
         </is>
       </c>
-      <c r="M22" t="inlineStr"/>
       <c r="N22" t="inlineStr">
         <is>
           <t>Beroperasi</t>
         </is>
       </c>
-      <c r="O22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
           <t>Normal</t>
         </is>
       </c>
-      <c r="Q22" t="inlineStr"/>
       <c r="R22" t="inlineStr">
         <is>
           <t>Jawa Barat</t>
         </is>
       </c>
-      <c r="S22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -1873,31 +1698,21 @@
           <t>150 kV</t>
         </is>
       </c>
-      <c r="G23" t="inlineStr"/>
-      <c r="H23" t="inlineStr"/>
-      <c r="I23" t="inlineStr"/>
-      <c r="J23" t="inlineStr"/>
-      <c r="K23" t="inlineStr"/>
-      <c r="L23" t="inlineStr"/>
-      <c r="M23" t="inlineStr"/>
       <c r="N23" t="inlineStr">
         <is>
           <t>Beroperasi</t>
         </is>
       </c>
-      <c r="O23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
           <t>Normal</t>
         </is>
       </c>
-      <c r="Q23" t="inlineStr"/>
       <c r="R23" t="inlineStr">
         <is>
           <t>Jawa Barat</t>
         </is>
       </c>
-      <c r="S23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -1926,31 +1741,21 @@
           <t>150 kV</t>
         </is>
       </c>
-      <c r="G24" t="inlineStr"/>
-      <c r="H24" t="inlineStr"/>
-      <c r="I24" t="inlineStr"/>
-      <c r="J24" t="inlineStr"/>
-      <c r="K24" t="inlineStr"/>
-      <c r="L24" t="inlineStr"/>
-      <c r="M24" t="inlineStr"/>
       <c r="N24" t="inlineStr">
         <is>
           <t>Beroperasi</t>
         </is>
       </c>
-      <c r="O24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
           <t>Normal</t>
         </is>
       </c>
-      <c r="Q24" t="inlineStr"/>
       <c r="R24" t="inlineStr">
         <is>
           <t>Jawa Barat</t>
         </is>
       </c>
-      <c r="S24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -1979,19 +1784,11 @@
           <t>150 kV</t>
         </is>
       </c>
-      <c r="G25" t="inlineStr"/>
-      <c r="H25" t="inlineStr"/>
-      <c r="I25" t="inlineStr"/>
-      <c r="J25" t="inlineStr"/>
-      <c r="K25" t="inlineStr"/>
-      <c r="L25" t="inlineStr"/>
-      <c r="M25" t="inlineStr"/>
       <c r="N25" t="inlineStr">
         <is>
           <t>Beroperasi</t>
         </is>
       </c>
-      <c r="O25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
           <t>Rawan</t>
@@ -2007,7 +1804,6 @@
           <t>Jawa Barat</t>
         </is>
       </c>
-      <c r="S25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -2036,23 +1832,16 @@
           <t>150 kV</t>
         </is>
       </c>
-      <c r="G26" t="inlineStr"/>
-      <c r="H26" t="inlineStr"/>
-      <c r="I26" t="inlineStr"/>
-      <c r="J26" t="inlineStr"/>
-      <c r="K26" t="inlineStr"/>
       <c r="L26" t="inlineStr">
         <is>
           <t>bus section + kopel</t>
         </is>
       </c>
-      <c r="M26" t="inlineStr"/>
       <c r="N26" t="inlineStr">
         <is>
           <t>Beroperasi</t>
         </is>
       </c>
-      <c r="O26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
           <t>Rawan</t>
@@ -2068,7 +1857,6 @@
           <t>Jawa Barat</t>
         </is>
       </c>
-      <c r="S26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -2097,31 +1885,21 @@
           <t>150 kV</t>
         </is>
       </c>
-      <c r="G27" t="inlineStr"/>
-      <c r="H27" t="inlineStr"/>
-      <c r="I27" t="inlineStr"/>
-      <c r="J27" t="inlineStr"/>
-      <c r="K27" t="inlineStr"/>
-      <c r="L27" t="inlineStr"/>
-      <c r="M27" t="inlineStr"/>
       <c r="N27" t="inlineStr">
         <is>
           <t>Beroperasi</t>
         </is>
       </c>
-      <c r="O27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
           <t>Normal</t>
         </is>
       </c>
-      <c r="Q27" t="inlineStr"/>
       <c r="R27" t="inlineStr">
         <is>
           <t>Jawa Barat</t>
         </is>
       </c>
-      <c r="S27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -2150,31 +1928,21 @@
           <t>150 kV</t>
         </is>
       </c>
-      <c r="G28" t="inlineStr"/>
-      <c r="H28" t="inlineStr"/>
-      <c r="I28" t="inlineStr"/>
-      <c r="J28" t="inlineStr"/>
-      <c r="K28" t="inlineStr"/>
-      <c r="L28" t="inlineStr"/>
-      <c r="M28" t="inlineStr"/>
       <c r="N28" t="inlineStr">
         <is>
           <t>Beroperasi</t>
         </is>
       </c>
-      <c r="O28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
           <t>Normal</t>
         </is>
       </c>
-      <c r="Q28" t="inlineStr"/>
       <c r="R28" t="inlineStr">
         <is>
           <t>Jawa Barat</t>
         </is>
       </c>
-      <c r="S28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -2203,23 +1971,16 @@
           <t>150 kV</t>
         </is>
       </c>
-      <c r="G29" t="inlineStr"/>
-      <c r="H29" t="inlineStr"/>
-      <c r="I29" t="inlineStr"/>
-      <c r="J29" t="inlineStr"/>
-      <c r="K29" t="inlineStr"/>
       <c r="L29" t="inlineStr">
         <is>
           <t>GI Simpul 4 subsistem; split busbar + kopel</t>
         </is>
       </c>
-      <c r="M29" t="inlineStr"/>
       <c r="N29" t="inlineStr">
         <is>
           <t>Beroperasi</t>
         </is>
       </c>
-      <c r="O29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
           <t>Rawan</t>
@@ -2235,7 +1996,6 @@
           <t>Jawa Barat</t>
         </is>
       </c>
-      <c r="S29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -2264,31 +2024,21 @@
           <t>150 kV</t>
         </is>
       </c>
-      <c r="G30" t="inlineStr"/>
-      <c r="H30" t="inlineStr"/>
-      <c r="I30" t="inlineStr"/>
-      <c r="J30" t="inlineStr"/>
-      <c r="K30" t="inlineStr"/>
-      <c r="L30" t="inlineStr"/>
-      <c r="M30" t="inlineStr"/>
       <c r="N30" t="inlineStr">
         <is>
           <t>Beroperasi</t>
         </is>
       </c>
-      <c r="O30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
           <t>Normal</t>
         </is>
       </c>
-      <c r="Q30" t="inlineStr"/>
       <c r="R30" t="inlineStr">
         <is>
           <t>Jawa Barat</t>
         </is>
       </c>
-      <c r="S30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -2317,17 +2067,11 @@
           <t>150 kV</t>
         </is>
       </c>
-      <c r="G31" t="inlineStr"/>
-      <c r="H31" t="inlineStr"/>
-      <c r="I31" t="inlineStr"/>
-      <c r="J31" t="inlineStr"/>
-      <c r="K31" t="inlineStr"/>
       <c r="L31" t="inlineStr">
         <is>
           <t>batas ke Subsistem Cibatu 3,4</t>
         </is>
       </c>
-      <c r="M31" t="inlineStr"/>
       <c r="N31" t="inlineStr">
         <is>
           <t>Beroperasi</t>
@@ -2343,13 +2087,11 @@
           <t>Normal</t>
         </is>
       </c>
-      <c r="Q31" t="inlineStr"/>
       <c r="R31" t="inlineStr">
         <is>
           <t>Jawa Barat</t>
         </is>
       </c>
-      <c r="S31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -2378,17 +2120,11 @@
           <t>150 kV</t>
         </is>
       </c>
-      <c r="G32" t="inlineStr"/>
-      <c r="H32" t="inlineStr"/>
-      <c r="I32" t="inlineStr"/>
-      <c r="J32" t="inlineStr"/>
-      <c r="K32" t="inlineStr"/>
       <c r="L32" t="inlineStr">
         <is>
           <t>batas ke Subsistem Cibatu 3,4</t>
         </is>
       </c>
-      <c r="M32" t="inlineStr"/>
       <c r="N32" t="inlineStr">
         <is>
           <t>Beroperasi</t>
@@ -2404,13 +2140,11 @@
           <t>Normal</t>
         </is>
       </c>
-      <c r="Q32" t="inlineStr"/>
       <c r="R32" t="inlineStr">
         <is>
           <t>Jawa Barat</t>
         </is>
       </c>
-      <c r="S32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -2439,17 +2173,11 @@
           <t>150 kV</t>
         </is>
       </c>
-      <c r="G33" t="inlineStr"/>
-      <c r="H33" t="inlineStr"/>
-      <c r="I33" t="inlineStr"/>
-      <c r="J33" t="inlineStr"/>
-      <c r="K33" t="inlineStr"/>
       <c r="L33" t="inlineStr">
         <is>
           <t>batas ke Subsistem Cibatu 3,4</t>
         </is>
       </c>
-      <c r="M33" t="inlineStr"/>
       <c r="N33" t="inlineStr">
         <is>
           <t>Beroperasi</t>
@@ -2465,13 +2193,11 @@
           <t>Normal</t>
         </is>
       </c>
-      <c r="Q33" t="inlineStr"/>
       <c r="R33" t="inlineStr">
         <is>
           <t>Jawa Barat</t>
         </is>
       </c>
-      <c r="S33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -2500,17 +2226,11 @@
           <t>150 kV</t>
         </is>
       </c>
-      <c r="G34" t="inlineStr"/>
-      <c r="H34" t="inlineStr"/>
-      <c r="I34" t="inlineStr"/>
-      <c r="J34" t="inlineStr"/>
-      <c r="K34" t="inlineStr"/>
       <c r="L34" t="inlineStr">
         <is>
           <t>batas ke Subsistem Cibatu 3,4</t>
         </is>
       </c>
-      <c r="M34" t="inlineStr"/>
       <c r="N34" t="inlineStr">
         <is>
           <t>Beroperasi</t>
@@ -2526,13 +2246,11 @@
           <t>Normal</t>
         </is>
       </c>
-      <c r="Q34" t="inlineStr"/>
       <c r="R34" t="inlineStr">
         <is>
           <t>Jawa Barat</t>
         </is>
       </c>
-      <c r="S34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -2561,17 +2279,11 @@
           <t>150 kV</t>
         </is>
       </c>
-      <c r="G35" t="inlineStr"/>
-      <c r="H35" t="inlineStr"/>
-      <c r="I35" t="inlineStr"/>
-      <c r="J35" t="inlineStr"/>
-      <c r="K35" t="inlineStr"/>
       <c r="L35" t="inlineStr">
         <is>
           <t>batas ke Subsistem New Tambun</t>
         </is>
       </c>
-      <c r="M35" t="inlineStr"/>
       <c r="N35" t="inlineStr">
         <is>
           <t>Beroperasi</t>
@@ -2587,13 +2299,11 @@
           <t>Normal</t>
         </is>
       </c>
-      <c r="Q35" t="inlineStr"/>
       <c r="R35" t="inlineStr">
         <is>
           <t>Jawa Barat</t>
         </is>
       </c>
-      <c r="S35" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -2700,7 +2410,6 @@
       <c r="A2" t="n">
         <v>1</v>
       </c>
-      <c r="B2" t="inlineStr"/>
       <c r="C2" t="inlineStr">
         <is>
           <t>Outlet PLTGU Bekasi Power</t>
@@ -2721,7 +2430,6 @@
           <t>150 kV</t>
         </is>
       </c>
-      <c r="G2" t="inlineStr"/>
       <c r="H2" t="n">
         <v>1</v>
       </c>
@@ -2735,8 +2443,6 @@
           <t>Normal</t>
         </is>
       </c>
-      <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
       <c r="M2" t="inlineStr">
         <is>
           <t>Jawa Barat</t>
@@ -2753,13 +2459,11 @@
           <t>Tidak</t>
         </is>
       </c>
-      <c r="Q2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
         <v>2</v>
       </c>
-      <c r="B3" t="inlineStr"/>
       <c r="C3" t="inlineStr">
         <is>
           <t>Outlet PLTGU Cikarang Listrindo</t>
@@ -2780,7 +2484,6 @@
           <t>150 kV</t>
         </is>
       </c>
-      <c r="G3" t="inlineStr"/>
       <c r="H3" t="n">
         <v>1</v>
       </c>
@@ -2794,8 +2497,6 @@
           <t>Normal</t>
         </is>
       </c>
-      <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
       <c r="M3" t="inlineStr">
         <is>
           <t>Jawa Barat</t>
@@ -2812,13 +2513,11 @@
           <t>Tidak</t>
         </is>
       </c>
-      <c r="Q3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
         <v>3</v>
       </c>
-      <c r="B4" t="inlineStr"/>
       <c r="C4" t="inlineStr">
         <is>
           <t>SUTT Cibatu - Maka Sri (arah SS Cibatu 3,4)</t>
@@ -2839,7 +2538,6 @@
           <t>150 kV</t>
         </is>
       </c>
-      <c r="G4" t="inlineStr"/>
       <c r="H4" t="n">
         <v>2</v>
       </c>
@@ -2853,8 +2551,6 @@
           <t>Normal</t>
         </is>
       </c>
-      <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
       <c r="M4" t="inlineStr">
         <is>
           <t>Jawa Barat</t>
@@ -2871,13 +2567,11 @@
           <t>Tidak</t>
         </is>
       </c>
-      <c r="Q4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
         <v>4</v>
       </c>
-      <c r="B5" t="inlineStr"/>
       <c r="C5" t="inlineStr">
         <is>
           <t>SUTT Cibatu - Suzuki (arah SS Cibatu 3,4)</t>
@@ -2898,7 +2592,6 @@
           <t>150 kV</t>
         </is>
       </c>
-      <c r="G5" t="inlineStr"/>
       <c r="H5" t="n">
         <v>2</v>
       </c>
@@ -2912,8 +2605,6 @@
           <t>Normal</t>
         </is>
       </c>
-      <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr"/>
       <c r="M5" t="inlineStr">
         <is>
           <t>Jawa Barat</t>
@@ -2930,13 +2621,11 @@
           <t>Tidak</t>
         </is>
       </c>
-      <c r="Q5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
         <v>5</v>
       </c>
-      <c r="B6" t="inlineStr"/>
       <c r="C6" t="inlineStr">
         <is>
           <t>SUTT Cibatu - Jababeka Usin</t>
@@ -2957,7 +2646,6 @@
           <t>150 kV</t>
         </is>
       </c>
-      <c r="G6" t="inlineStr"/>
       <c r="H6" t="n">
         <v>2</v>
       </c>
@@ -2971,8 +2659,6 @@
           <t>Normal</t>
         </is>
       </c>
-      <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr"/>
       <c r="M6" t="inlineStr">
         <is>
           <t>Jawa Barat</t>
@@ -2989,13 +2675,11 @@
           <t>Tidak</t>
         </is>
       </c>
-      <c r="Q6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
         <v>6</v>
       </c>
-      <c r="B7" t="inlineStr"/>
       <c r="C7" t="inlineStr">
         <is>
           <t>SUTT Cibatu - Cilegsi</t>
@@ -3016,7 +2700,6 @@
           <t>150 kV</t>
         </is>
       </c>
-      <c r="G7" t="inlineStr"/>
       <c r="H7" t="n">
         <v>2</v>
       </c>
@@ -3030,8 +2713,6 @@
           <t>Normal</t>
         </is>
       </c>
-      <c r="K7" t="inlineStr"/>
-      <c r="L7" t="inlineStr"/>
       <c r="M7" t="inlineStr">
         <is>
           <t>Jawa Barat</t>
@@ -3048,7 +2729,6 @@
           <t>Tidak</t>
         </is>
       </c>
-      <c r="Q7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -3079,7 +2759,6 @@
           <t>150 kV</t>
         </is>
       </c>
-      <c r="G8" t="inlineStr"/>
       <c r="H8" t="n">
         <v>2</v>
       </c>
@@ -3093,8 +2772,6 @@
           <t>Sangat Rawan</t>
         </is>
       </c>
-      <c r="K8" t="inlineStr"/>
-      <c r="L8" t="inlineStr"/>
       <c r="M8" t="inlineStr">
         <is>
           <t>Jawa Barat</t>
@@ -3111,13 +2788,11 @@
           <t>Tidak</t>
         </is>
       </c>
-      <c r="Q8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
         <v>8</v>
       </c>
-      <c r="B9" t="inlineStr"/>
       <c r="C9" t="inlineStr">
         <is>
           <t>SUTT Bekasi Power - Jababeka</t>
@@ -3138,7 +2813,6 @@
           <t>150 kV</t>
         </is>
       </c>
-      <c r="G9" t="inlineStr"/>
       <c r="H9" t="n">
         <v>2</v>
       </c>
@@ -3152,8 +2826,6 @@
           <t>Normal</t>
         </is>
       </c>
-      <c r="K9" t="inlineStr"/>
-      <c r="L9" t="inlineStr"/>
       <c r="M9" t="inlineStr">
         <is>
           <t>Jawa Barat</t>
@@ -3170,13 +2842,11 @@
           <t>Tidak</t>
         </is>
       </c>
-      <c r="Q9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
         <v>9</v>
       </c>
-      <c r="B10" t="inlineStr"/>
       <c r="C10" t="inlineStr">
         <is>
           <t>SUTT Cikarang Listrindo - Cikarang</t>
@@ -3197,7 +2867,6 @@
           <t>150 kV</t>
         </is>
       </c>
-      <c r="G10" t="inlineStr"/>
       <c r="H10" t="n">
         <v>2</v>
       </c>
@@ -3211,8 +2880,6 @@
           <t>Normal</t>
         </is>
       </c>
-      <c r="K10" t="inlineStr"/>
-      <c r="L10" t="inlineStr"/>
       <c r="M10" t="inlineStr">
         <is>
           <t>Jawa Barat</t>
@@ -3229,13 +2896,11 @@
           <t>Tidak</t>
         </is>
       </c>
-      <c r="Q10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
         <v>10</v>
       </c>
-      <c r="B11" t="inlineStr"/>
       <c r="C11" t="inlineStr">
         <is>
           <t>SUTT Hankook - Rejosari</t>
@@ -3256,7 +2921,6 @@
           <t>150 kV</t>
         </is>
       </c>
-      <c r="G11" t="inlineStr"/>
       <c r="H11" t="n">
         <v>2</v>
       </c>
@@ -3270,8 +2934,6 @@
           <t>Normal</t>
         </is>
       </c>
-      <c r="K11" t="inlineStr"/>
-      <c r="L11" t="inlineStr"/>
       <c r="M11" t="inlineStr">
         <is>
           <t>Jawa Barat</t>
@@ -3288,13 +2950,11 @@
           <t>Tidak</t>
         </is>
       </c>
-      <c r="Q11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
         <v>11</v>
       </c>
-      <c r="B12" t="inlineStr"/>
       <c r="C12" t="inlineStr">
         <is>
           <t>SUTT Jababeka - Meyko Makmur</t>
@@ -3315,7 +2975,6 @@
           <t>150 kV</t>
         </is>
       </c>
-      <c r="G12" t="inlineStr"/>
       <c r="H12" t="n">
         <v>2</v>
       </c>
@@ -3329,8 +2988,6 @@
           <t>Normal</t>
         </is>
       </c>
-      <c r="K12" t="inlineStr"/>
-      <c r="L12" t="inlineStr"/>
       <c r="M12" t="inlineStr">
         <is>
           <t>Jawa Barat</t>
@@ -3347,7 +3004,6 @@
           <t>Tidak</t>
         </is>
       </c>
-      <c r="Q12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -3378,7 +3034,6 @@
           <t>150 kV</t>
         </is>
       </c>
-      <c r="G13" t="inlineStr"/>
       <c r="H13" t="n">
         <v>2</v>
       </c>
@@ -3392,8 +3047,6 @@
           <t>Sangat Rawan</t>
         </is>
       </c>
-      <c r="K13" t="inlineStr"/>
-      <c r="L13" t="inlineStr"/>
       <c r="M13" t="inlineStr">
         <is>
           <t>Jawa Barat</t>
@@ -3410,7 +3063,6 @@
           <t>Tidak</t>
         </is>
       </c>
-      <c r="Q13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -3441,7 +3093,6 @@
           <t>150 kV</t>
         </is>
       </c>
-      <c r="G14" t="inlineStr"/>
       <c r="H14" t="n">
         <v>2</v>
       </c>
@@ -3455,8 +3106,6 @@
           <t>Sangat Rawan</t>
         </is>
       </c>
-      <c r="K14" t="inlineStr"/>
-      <c r="L14" t="inlineStr"/>
       <c r="M14" t="inlineStr">
         <is>
           <t>Jawa Barat</t>
@@ -3473,13 +3122,11 @@
           <t>Tidak</t>
         </is>
       </c>
-      <c r="Q14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
         <v>14</v>
       </c>
-      <c r="B15" t="inlineStr"/>
       <c r="C15" t="inlineStr">
         <is>
           <t>SUTT Deltamas - Sukamahi</t>
@@ -3500,7 +3147,6 @@
           <t>150 kV</t>
         </is>
       </c>
-      <c r="G15" t="inlineStr"/>
       <c r="H15" t="n">
         <v>2</v>
       </c>
@@ -3514,8 +3160,6 @@
           <t>Normal</t>
         </is>
       </c>
-      <c r="K15" t="inlineStr"/>
-      <c r="L15" t="inlineStr"/>
       <c r="M15" t="inlineStr">
         <is>
           <t>Jawa Barat</t>
@@ -3532,7 +3176,6 @@
           <t>Tidak</t>
         </is>
       </c>
-      <c r="Q15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -3563,7 +3206,6 @@
           <t>150 kV</t>
         </is>
       </c>
-      <c r="G16" t="inlineStr"/>
       <c r="H16" t="n">
         <v>2</v>
       </c>
@@ -3577,8 +3219,6 @@
           <t>Sangat Rawan</t>
         </is>
       </c>
-      <c r="K16" t="inlineStr"/>
-      <c r="L16" t="inlineStr"/>
       <c r="M16" t="inlineStr">
         <is>
           <t>Jawa Barat</t>
@@ -3595,13 +3235,11 @@
           <t>Tidak</t>
         </is>
       </c>
-      <c r="Q16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
         <v>16</v>
       </c>
-      <c r="B17" t="inlineStr"/>
       <c r="C17" t="inlineStr">
         <is>
           <t>SUTT Sukamahi - THK</t>
@@ -3622,7 +3260,6 @@
           <t>150 kV</t>
         </is>
       </c>
-      <c r="G17" t="inlineStr"/>
       <c r="H17" t="n">
         <v>2</v>
       </c>
@@ -3636,8 +3273,6 @@
           <t>Normal</t>
         </is>
       </c>
-      <c r="K17" t="inlineStr"/>
-      <c r="L17" t="inlineStr"/>
       <c r="M17" t="inlineStr">
         <is>
           <t>Jawa Barat</t>
@@ -3654,13 +3289,11 @@
           <t>Tidak</t>
         </is>
       </c>
-      <c r="Q17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
         <v>17</v>
       </c>
-      <c r="B18" t="inlineStr"/>
       <c r="C18" t="inlineStr">
         <is>
           <t>SUTT Sukamahi - Mega Kaya</t>
@@ -3681,7 +3314,6 @@
           <t>150 kV</t>
         </is>
       </c>
-      <c r="G18" t="inlineStr"/>
       <c r="H18" t="n">
         <v>2</v>
       </c>
@@ -3695,8 +3327,6 @@
           <t>Normal</t>
         </is>
       </c>
-      <c r="K18" t="inlineStr"/>
-      <c r="L18" t="inlineStr"/>
       <c r="M18" t="inlineStr">
         <is>
           <t>Jawa Barat</t>
@@ -3713,13 +3343,11 @@
           <t>Tidak</t>
         </is>
       </c>
-      <c r="Q18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
         <v>18</v>
       </c>
-      <c r="B19" t="inlineStr"/>
       <c r="C19" t="inlineStr">
         <is>
           <t>SUTT Gandamekar - Tambun (arah SS New Tambun)</t>
@@ -3740,7 +3368,6 @@
           <t>150 kV</t>
         </is>
       </c>
-      <c r="G19" t="inlineStr"/>
       <c r="H19" t="n">
         <v>2</v>
       </c>
@@ -3754,8 +3381,6 @@
           <t>Normal</t>
         </is>
       </c>
-      <c r="K19" t="inlineStr"/>
-      <c r="L19" t="inlineStr"/>
       <c r="M19" t="inlineStr">
         <is>
           <t>Jawa Barat</t>
@@ -3772,13 +3397,11 @@
           <t>Tidak</t>
         </is>
       </c>
-      <c r="Q19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
         <v>19</v>
       </c>
-      <c r="B20" t="inlineStr"/>
       <c r="C20" t="inlineStr">
         <is>
           <t>SUTT Mega Kaya - Pinayungan</t>
@@ -3799,7 +3422,6 @@
           <t>150 kV</t>
         </is>
       </c>
-      <c r="G20" t="inlineStr"/>
       <c r="H20" t="n">
         <v>2</v>
       </c>
@@ -3813,8 +3435,6 @@
           <t>Normal</t>
         </is>
       </c>
-      <c r="K20" t="inlineStr"/>
-      <c r="L20" t="inlineStr"/>
       <c r="M20" t="inlineStr">
         <is>
           <t>Jawa Barat</t>
@@ -3831,13 +3451,11 @@
           <t>Tidak</t>
         </is>
       </c>
-      <c r="Q20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
         <v>20</v>
       </c>
-      <c r="B21" t="inlineStr"/>
       <c r="C21" t="inlineStr">
         <is>
           <t>SUTT Pinayungan - Tegal Herang</t>
@@ -3858,7 +3476,6 @@
           <t>150 kV</t>
         </is>
       </c>
-      <c r="G21" t="inlineStr"/>
       <c r="H21" t="n">
         <v>2</v>
       </c>
@@ -3872,8 +3489,6 @@
           <t>Normal</t>
         </is>
       </c>
-      <c r="K21" t="inlineStr"/>
-      <c r="L21" t="inlineStr"/>
       <c r="M21" t="inlineStr">
         <is>
           <t>Jawa Barat</t>
@@ -3890,13 +3505,11 @@
           <t>Tidak</t>
         </is>
       </c>
-      <c r="Q21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
         <v>21</v>
       </c>
-      <c r="B22" t="inlineStr"/>
       <c r="C22" t="inlineStr">
         <is>
           <t>SUTT Pinayungan - Maka Sri (arah SS Cibatu 3,4)</t>
@@ -3917,7 +3530,6 @@
           <t>150 kV</t>
         </is>
       </c>
-      <c r="G22" t="inlineStr"/>
       <c r="H22" t="n">
         <v>2</v>
       </c>
@@ -3931,8 +3543,6 @@
           <t>Normal</t>
         </is>
       </c>
-      <c r="K22" t="inlineStr"/>
-      <c r="L22" t="inlineStr"/>
       <c r="M22" t="inlineStr">
         <is>
           <t>Jawa Barat</t>
@@ -3949,13 +3559,11 @@
           <t>Tidak</t>
         </is>
       </c>
-      <c r="Q22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
         <v>22</v>
       </c>
-      <c r="B23" t="inlineStr"/>
       <c r="C23" t="inlineStr">
         <is>
           <t>SUTT Pinayungan - Peruri (arah SS Cibatu 3,4)</t>
@@ -3976,7 +3584,6 @@
           <t>150 kV</t>
         </is>
       </c>
-      <c r="G23" t="inlineStr"/>
       <c r="H23" t="n">
         <v>2</v>
       </c>
@@ -3990,8 +3597,6 @@
           <t>Normal</t>
         </is>
       </c>
-      <c r="K23" t="inlineStr"/>
-      <c r="L23" t="inlineStr"/>
       <c r="M23" t="inlineStr">
         <is>
           <t>Jawa Barat</t>
@@ -4008,13 +3613,11 @@
           <t>Tidak</t>
         </is>
       </c>
-      <c r="Q23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
         <v>23</v>
       </c>
-      <c r="B24" t="inlineStr"/>
       <c r="C24" t="inlineStr">
         <is>
           <t>SUTT Pinayungan - Purwamaya (arah SS Cibatu 3,4)</t>
@@ -4035,7 +3638,6 @@
           <t>150 kV</t>
         </is>
       </c>
-      <c r="G24" t="inlineStr"/>
       <c r="H24" t="n">
         <v>2</v>
       </c>
@@ -4049,8 +3651,6 @@
           <t>Normal</t>
         </is>
       </c>
-      <c r="K24" t="inlineStr"/>
-      <c r="L24" t="inlineStr"/>
       <c r="M24" t="inlineStr">
         <is>
           <t>Jawa Barat</t>
@@ -4067,7 +3667,6 @@
           <t>Tidak</t>
         </is>
       </c>
-      <c r="Q24" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -4172,8 +3771,6 @@
           <t>Beroperasi</t>
         </is>
       </c>
-      <c r="I2" t="inlineStr"/>
-      <c r="J2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -4212,8 +3809,6 @@
           <t>Beroperasi</t>
         </is>
       </c>
-      <c r="I3" t="inlineStr"/>
-      <c r="J3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -4252,8 +3847,6 @@
           <t>Beroperasi</t>
         </is>
       </c>
-      <c r="I4" t="inlineStr"/>
-      <c r="J4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -4292,8 +3885,6 @@
           <t>Beroperasi</t>
         </is>
       </c>
-      <c r="I5" t="inlineStr"/>
-      <c r="J5" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -4412,7 +4003,7 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Jangka Pendek: Pembangunan GISTET Tambun IBT 3 &amp; 4 beserta outletnya, RUPTL 2025-2034, COD Tahun 2025</t>
+          <t>Jangka Pendek: Pembangunan GISTET Tambun IBT 3 &amp; 4 beserta outletnya, RUPTL 2025 -2034, COD Tahun 2025</t>
         </is>
       </c>
     </row>
@@ -4447,7 +4038,7 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Jangka Pendek: Pembangunan Outlet GITET Sukatani Penghantar 150 kV Sukatani-Fajar SW, RUPTL 2025 - 2034, COD Tahun 2027 (update terkendala lahan pada sisi GI Fajar SW)</t>
+          <t>Jangka Pendek: Pembangunan Outlet GITET Sukatani Penghantar 150 kV Sukatani -Fajar SW, RUPTL 2025 - 2034, COD Tahun 2027 (update terkendala lahan pada sisi GI Fajar SW)</t>
         </is>
       </c>
     </row>
@@ -4482,7 +4073,7 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Jangka Pendek: 1. Rekonduktoring Outlet GITET Sukatani (Kosambi Baru- Sukatani). Sesuai RUPTL 2025-2034 COD 2025. 2. Pembangunan GISTET Tambun IBT 3 &amp; 4 beserta outletnya, RUPTL 2025 - 2034, COD Tahun 2025</t>
+          <t>Jangka Pendek: 1. Rekonduktoring Outlet GITET Sukatani (Kosambi Baru- Sukatani). Sesuai RUPTL 2025 -2034 COD 2025. 2. Pembangunan GISTET Tambun IBT 3 &amp; 4 beserta outletnya, RUPTL 2025 - 2034, COD Tahun 2025</t>
         </is>
       </c>
     </row>
@@ -4517,7 +4108,7 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Jangka Pendek: Pembangunan GISTET Tambun IBT 3 &amp; 4 beserta outletnya, RUPTL 2025-2034, COD Tahun 2025</t>
+          <t>Jangka Pendek: Pembangunan GISTET Tambun IBT 3 &amp; 4 beserta outletnya, RUPTL 2025 -2034, COD Tahun 2025</t>
         </is>
       </c>
     </row>
@@ -4552,7 +4143,7 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Jangka Pendek: Pembangunan GISTET Tambun IBT 3 &amp; 4 beserta outletnya, RUPTL 2025-2034, COD Tahun 2025</t>
+          <t>Jangka Pendek: Pembangunan GISTET Tambun IBT 3 &amp; 4 beserta outletnya, RUPTL 2025 -2034, COD Tahun 2025</t>
         </is>
       </c>
     </row>
@@ -4587,7 +4178,7 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Jangka Pendek: Pembangunan GITET Karawang (2x500 MVA) dan outletnya (SUTT Karawang-Margakarya), RUPTL 2025-2034, COD 2027</t>
+          <t>Jangka Pendek: Pembangunan GITET Karawang (2x500 MVA) dan outletnya (SUTT Karawang -Margakarya), RUPTL 2025 -2034, COD 2027</t>
         </is>
       </c>
     </row>
@@ -4622,7 +4213,7 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Jangka Pendek: Penambahan 2 Bus Section dan kopel kedua GI 150 kV Margakarya. Sesuai RUPTL 2025 -2034, COD 2027</t>
+          <t>Jangka Pendek: Penambahan 2 Bus Section dan kopel kedua GI 150 kV Margakarya. Sesuai RUPTL 2025 - 2034, COD 2027</t>
         </is>
       </c>
     </row>
